--- a/Conversões.xlsx
+++ b/Conversões.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="47">
   <si>
     <t>Código Produto</t>
   </si>
@@ -77,12 +77,93 @@
   </si>
   <si>
     <t>Negócio</t>
+  </si>
+  <si>
+    <t>YSI103740Y</t>
+  </si>
+  <si>
+    <t>YSI109813Y</t>
+  </si>
+  <si>
+    <t>YSI1FD560Y</t>
+  </si>
+  <si>
+    <t>SENSOR YSI IDS COMBINADO DE PH E TEMPERATURA - CABO DE 1,5 METROS</t>
+  </si>
+  <si>
+    <t>SUPORTE PARA SENSORES IDS PARA INSTRUMENTOS YSI MULTILAB</t>
+  </si>
+  <si>
+    <t>ANALISADOR DE BANCADA YSI MULTILAB IDS (DUPLO CANAL)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>PVEN - PEDIDO DE VENDA</t>
+  </si>
+  <si>
+    <t>999999</t>
+  </si>
+  <si>
+    <t>FATURADO</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>SAMANTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KELLY AMARAL BISPO                      </t>
+  </si>
+  <si>
+    <t>HIDROLOGIA</t>
+  </si>
+  <si>
+    <t>8648</t>
+  </si>
+  <si>
+    <t>BRK AMBIENTAL - RIO CLARO S.A.</t>
+  </si>
+  <si>
+    <t>RIO CLARO</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>Reposição</t>
+  </si>
+  <si>
+    <t>Produto</t>
+  </si>
+  <si>
+    <t>Sensor</t>
+  </si>
+  <si>
+    <t>Acessório</t>
+  </si>
+  <si>
+    <t>MULTILAB</t>
+  </si>
+  <si>
+    <t>Sonda Portátil</t>
+  </si>
+  <si>
+    <t>Sonda Serie MultiLab</t>
+  </si>
+  <si>
+    <t>Hidrologia</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -135,11 +216,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
@@ -502,6 +584,192 @@
         <v>20</v>
       </c>
     </row>
+    <row r="2" spans="1:21">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="2">
+        <v>45880</v>
+      </c>
+      <c r="H2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T2" t="s">
+        <v>44</v>
+      </c>
+      <c r="U2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="2">
+        <v>45880</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>38</v>
+      </c>
+      <c r="R3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" t="s">
+        <v>42</v>
+      </c>
+      <c r="T3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="2">
+        <v>45880</v>
+      </c>
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>38</v>
+      </c>
+      <c r="R4" t="s">
+        <v>40</v>
+      </c>
+      <c r="S4" t="s">
+        <v>43</v>
+      </c>
+      <c r="T4" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Conversões.xlsx
+++ b/Conversões.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="30">
   <si>
     <t>Código Produto</t>
   </si>
@@ -22,9 +22,6 @@
     <t>Descrição Produto</t>
   </si>
   <si>
-    <t>Qtde Atendida</t>
-  </si>
-  <si>
     <t>Operação</t>
   </si>
   <si>
@@ -52,21 +49,9 @@
     <t>Gerente Comercial-Pedido</t>
   </si>
   <si>
-    <t>Aplicação Mat./Serv.</t>
-  </si>
-  <si>
     <t>Cliente</t>
   </si>
   <si>
-    <t>Nome Cliente</t>
-  </si>
-  <si>
-    <t>Cidade</t>
-  </si>
-  <si>
-    <t>UF</t>
-  </si>
-  <si>
     <t>Tipo de Mercadoria</t>
   </si>
   <si>
@@ -79,28 +64,13 @@
     <t>Negócio</t>
   </si>
   <si>
-    <t>YSI103740Y</t>
-  </si>
-  <si>
-    <t>YSI109813Y</t>
-  </si>
-  <si>
-    <t>YSI1FD560Y</t>
-  </si>
-  <si>
-    <t>SENSOR YSI IDS COMBINADO DE PH E TEMPERATURA - CABO DE 1,5 METROS</t>
-  </si>
-  <si>
-    <t>SUPORTE PARA SENSORES IDS PARA INSTRUMENTOS YSI MULTILAB</t>
-  </si>
-  <si>
-    <t>ANALISADOR DE BANCADA YSI MULTILAB IDS (DUPLO CANAL)</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>PVEN - PEDIDO DE VENDA</t>
+    <t>QED-AP4-RET</t>
+  </si>
+  <si>
+    <t>Teste Retenção (Neimar)</t>
+  </si>
+  <si>
+    <t>PVEN</t>
   </si>
   <si>
     <t>999999</t>
@@ -112,49 +82,28 @@
     <t>100</t>
   </si>
   <si>
-    <t>SAMANTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KELLY AMARAL BISPO                      </t>
-  </si>
-  <si>
-    <t>HIDROLOGIA</t>
-  </si>
-  <si>
-    <t>8648</t>
-  </si>
-  <si>
-    <t>BRK AMBIENTAL - RIO CLARO S.A.</t>
-  </si>
-  <si>
-    <t>RIO CLARO</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>Reposição</t>
+    <t>DENER.MARTINS</t>
+  </si>
+  <si>
+    <t>Cliente Teste1</t>
+  </si>
+  <si>
+    <t>Cliente Teste2</t>
+  </si>
+  <si>
+    <t>Cliente Teste3</t>
   </si>
   <si>
     <t>Produto</t>
   </si>
   <si>
-    <t>Sensor</t>
-  </si>
-  <si>
-    <t>Acessório</t>
-  </si>
-  <si>
-    <t>MULTILAB</t>
-  </si>
-  <si>
-    <t>Sonda Portátil</t>
-  </si>
-  <si>
-    <t>Sonda Serie MultiLab</t>
-  </si>
-  <si>
-    <t>Hidrologia</t>
+    <t>Auto Pump</t>
+  </si>
+  <si>
+    <t>Elevador de Liquidos Fixo</t>
+  </si>
+  <si>
+    <t>Remediação</t>
   </si>
 </sst>
 </file>
@@ -516,10 +465,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -568,206 +517,269 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="C2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="E2" t="s">
         <v>20</v>
       </c>
+      <c r="F2" s="2">
+        <v>45918</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="2" spans="1:21">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="2">
+        <v>45918</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
         <v>24</v>
       </c>
-      <c r="C2" t="s">
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" t="s">
         <v>27</v>
       </c>
-      <c r="D2" t="s">
+      <c r="O3" t="s">
         <v>28</v>
       </c>
-      <c r="E2" t="s">
+      <c r="P3" t="s">
         <v>29</v>
       </c>
-      <c r="F2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="2">
-        <v>45880</v>
-      </c>
-      <c r="H2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P2" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R2" t="s">
-        <v>39</v>
-      </c>
-      <c r="S2" t="s">
-        <v>41</v>
-      </c>
-      <c r="T2" t="s">
-        <v>44</v>
-      </c>
-      <c r="U2" t="s">
-        <v>46</v>
-      </c>
     </row>
-    <row r="3" spans="1:21">
-      <c r="A3" t="s">
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="2">
+        <v>45918</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
         <v>22</v>
       </c>
-      <c r="B3" t="s">
+      <c r="L4" t="s">
         <v>25</v>
       </c>
-      <c r="C3" t="s">
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" t="s">
         <v>27</v>
       </c>
-      <c r="D3" t="s">
+      <c r="O4" t="s">
         <v>28</v>
       </c>
-      <c r="E3" t="s">
+      <c r="P4" t="s">
         <v>29</v>
       </c>
-      <c r="F3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="2">
-        <v>45880</v>
-      </c>
-      <c r="H3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M3" t="s">
-        <v>34</v>
-      </c>
-      <c r="N3" t="s">
-        <v>35</v>
-      </c>
-      <c r="O3" t="s">
-        <v>36</v>
-      </c>
-      <c r="P3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>38</v>
-      </c>
-      <c r="R3" t="s">
-        <v>39</v>
-      </c>
-      <c r="S3" t="s">
-        <v>42</v>
-      </c>
-      <c r="T3" t="s">
-        <v>44</v>
-      </c>
-      <c r="U3" t="s">
-        <v>46</v>
-      </c>
     </row>
-    <row r="4" spans="1:21">
-      <c r="A4" t="s">
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="2">
+        <v>45918</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s">
         <v>23</v>
       </c>
-      <c r="B4" t="s">
+      <c r="M5" t="s">
         <v>26</v>
       </c>
-      <c r="C4" t="s">
+      <c r="N5" t="s">
         <v>27</v>
       </c>
-      <c r="D4" t="s">
+      <c r="O5" t="s">
         <v>28</v>
       </c>
-      <c r="E4" t="s">
+      <c r="P5" t="s">
         <v>29</v>
       </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="2">
-        <v>45880</v>
-      </c>
-      <c r="H4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" t="s">
-        <v>35</v>
-      </c>
-      <c r="O4" t="s">
-        <v>36</v>
-      </c>
-      <c r="P4" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>38</v>
-      </c>
-      <c r="R4" t="s">
-        <v>40</v>
-      </c>
-      <c r="S4" t="s">
-        <v>43</v>
-      </c>
-      <c r="T4" t="s">
-        <v>45</v>
-      </c>
-      <c r="U4" t="s">
-        <v>46</v>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="2">
+        <v>45918</v>
+      </c>
+      <c r="G6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45918</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Conversões.xlsx
+++ b/Conversões.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="47">
   <si>
     <t>Código Produto</t>
   </si>
@@ -22,6 +22,9 @@
     <t>Descrição Produto</t>
   </si>
   <si>
+    <t>Qtde Atendida</t>
+  </si>
+  <si>
     <t>Operação</t>
   </si>
   <si>
@@ -49,9 +52,21 @@
     <t>Gerente Comercial-Pedido</t>
   </si>
   <si>
+    <t>Aplicação Mat./Serv.</t>
+  </si>
+  <si>
     <t>Cliente</t>
   </si>
   <si>
+    <t>Nome Cliente</t>
+  </si>
+  <si>
+    <t>Cidade</t>
+  </si>
+  <si>
+    <t>UF</t>
+  </si>
+  <si>
     <t>Tipo de Mercadoria</t>
   </si>
   <si>
@@ -64,13 +79,28 @@
     <t>Negócio</t>
   </si>
   <si>
-    <t>QED-AP4-RET</t>
-  </si>
-  <si>
-    <t>Teste Retenção (Neimar)</t>
-  </si>
-  <si>
-    <t>PVEN</t>
+    <t>YSI103740Y</t>
+  </si>
+  <si>
+    <t>YSI109813Y</t>
+  </si>
+  <si>
+    <t>YSI1FD560Y</t>
+  </si>
+  <si>
+    <t>SENSOR YSI IDS COMBINADO DE PH E TEMPERATURA - CABO DE 1,5 METROS</t>
+  </si>
+  <si>
+    <t>SUPORTE PARA SENSORES IDS PARA INSTRUMENTOS YSI MULTILAB</t>
+  </si>
+  <si>
+    <t>ANALISADOR DE BANCADA YSI MULTILAB IDS (DUPLO CANAL)</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>PVEN - PEDIDO DE VENDA</t>
   </si>
   <si>
     <t>999999</t>
@@ -82,28 +112,49 @@
     <t>100</t>
   </si>
   <si>
-    <t>DENER.MARTINS</t>
-  </si>
-  <si>
-    <t>Cliente Teste1</t>
-  </si>
-  <si>
-    <t>Cliente Teste2</t>
-  </si>
-  <si>
-    <t>Cliente Teste3</t>
+    <t>SAMANTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KELLY AMARAL BISPO                      </t>
+  </si>
+  <si>
+    <t>HIDROLOGIA</t>
+  </si>
+  <si>
+    <t>8648</t>
+  </si>
+  <si>
+    <t>BRK AMBIENTAL - RIO CLARO S.A.</t>
+  </si>
+  <si>
+    <t>RIO CLARO</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>Reposição</t>
   </si>
   <si>
     <t>Produto</t>
   </si>
   <si>
-    <t>Auto Pump</t>
-  </si>
-  <si>
-    <t>Elevador de Liquidos Fixo</t>
-  </si>
-  <si>
-    <t>Remediação</t>
+    <t>Sensor</t>
+  </si>
+  <si>
+    <t>Acessório</t>
+  </si>
+  <si>
+    <t>MULTILAB</t>
+  </si>
+  <si>
+    <t>Sonda Portátil</t>
+  </si>
+  <si>
+    <t>Sonda Serie MultiLab</t>
+  </si>
+  <si>
+    <t>Hidrologia</t>
   </si>
 </sst>
 </file>
@@ -465,10 +516,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -517,269 +568,206 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="2">
-        <v>45918</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
+        <v>29</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="2">
+        <v>45880</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" t="s">
+        <v>35</v>
+      </c>
+      <c r="O2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T2" t="s">
+        <v>44</v>
+      </c>
+      <c r="U2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" t="s">
         <v>22</v>
       </c>
-      <c r="L2" t="s">
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="2">
+        <v>45880</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>38</v>
+      </c>
+      <c r="R3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" t="s">
+        <v>42</v>
+      </c>
+      <c r="T3" t="s">
+        <v>44</v>
+      </c>
+      <c r="U3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" t="s">
         <v>23</v>
       </c>
-      <c r="M2" t="s">
+      <c r="B4" t="s">
         <v>26</v>
       </c>
-      <c r="N2" t="s">
+      <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="O2" t="s">
+      <c r="D4" t="s">
         <v>28</v>
       </c>
-      <c r="P2" t="s">
+      <c r="E4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="2">
-        <v>45918</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" t="s">
-        <v>28</v>
-      </c>
-      <c r="P3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="2">
-        <v>45918</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="2">
+        <v>45880</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="I4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4" t="s">
-        <v>25</v>
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" t="s">
+        <v>33</v>
       </c>
       <c r="M4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="N4" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="O4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="2">
-        <v>45918</v>
-      </c>
-      <c r="G5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="2">
-        <v>45918</v>
-      </c>
-      <c r="G6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" t="s">
-        <v>28</v>
-      </c>
-      <c r="P6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="2">
-        <v>45918</v>
-      </c>
-      <c r="G7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M7" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" t="s">
-        <v>27</v>
-      </c>
-      <c r="O7" t="s">
-        <v>28</v>
-      </c>
-      <c r="P7" t="s">
-        <v>29</v>
+        <v>37</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>38</v>
+      </c>
+      <c r="R4" t="s">
+        <v>40</v>
+      </c>
+      <c r="S4" t="s">
+        <v>43</v>
+      </c>
+      <c r="T4" t="s">
+        <v>45</v>
+      </c>
+      <c r="U4" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Conversões.xlsx
+++ b/Conversões.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="51">
   <si>
     <t>Código Produto</t>
   </si>
@@ -79,31 +79,46 @@
     <t>Negócio</t>
   </si>
   <si>
-    <t>YSI103740Y</t>
-  </si>
-  <si>
-    <t>YSI109813Y</t>
-  </si>
-  <si>
-    <t>YSI1FD560Y</t>
-  </si>
-  <si>
-    <t>SENSOR YSI IDS COMBINADO DE PH E TEMPERATURA - CABO DE 1,5 METROS</t>
-  </si>
-  <si>
-    <t>SUPORTE PARA SENSORES IDS PARA INSTRUMENTOS YSI MULTILAB</t>
-  </si>
-  <si>
-    <t>ANALISADOR DE BANCADA YSI MULTILAB IDS (DUPLO CANAL)</t>
+    <t>HONMMS-G2</t>
+  </si>
+  <si>
+    <t>HONMMS-TR</t>
+  </si>
+  <si>
+    <t>HONMMS-D2</t>
+  </si>
+  <si>
+    <t>ANGLTA2051WJ24V-IND</t>
+  </si>
+  <si>
+    <t>HONMMT-01</t>
+  </si>
+  <si>
+    <t>SENSOR ELETROQUIMICO DE H2 PARA ANALISADOR DE GÁS MODELO MIDAS M</t>
+  </si>
+  <si>
+    <t>SENSOR IR DE CO2 PARA ANALISADOR DE GÁS MODELO MIDAS M</t>
+  </si>
+  <si>
+    <t>SENSOR DE OXIGÊNIO PARA USO NO ANALISADOR DE GASES MODELO MIDAS M</t>
+  </si>
+  <si>
+    <t>SIRENE P/ SISTEMA DE DETECÇÃO FIXA SAV-C 24V</t>
+  </si>
+  <si>
+    <t>ANALISADOR FIXO PARA 4 GASES - MODELO MIDAS M</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>PVEN - PEDIDO DE VENDA</t>
   </si>
   <si>
-    <t>999999</t>
+    <t>133701</t>
   </si>
   <si>
     <t>FATURADO</t>
@@ -112,22 +127,22 @@
     <t>100</t>
   </si>
   <si>
-    <t>SAMANTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KELLY AMARAL BISPO                      </t>
-  </si>
-  <si>
-    <t>HIDROLOGIA</t>
-  </si>
-  <si>
-    <t>8648</t>
-  </si>
-  <si>
-    <t>BRK AMBIENTAL - RIO CLARO S.A.</t>
-  </si>
-  <si>
-    <t>RIO CLARO</t>
+    <t>ANDREY.ANDRADE</t>
+  </si>
+  <si>
+    <t>LEONARDO DO CARMO</t>
+  </si>
+  <si>
+    <t>DEPART. DETECÇÃO FIXA GASES</t>
+  </si>
+  <si>
+    <t>22853</t>
+  </si>
+  <si>
+    <t>AMYRIS FERMENTACAO DE PERFORMANCE LTDA</t>
+  </si>
+  <si>
+    <t>BARRA BONITA</t>
   </si>
   <si>
     <t>SP</t>
@@ -145,16 +160,13 @@
     <t>Acessório</t>
   </si>
   <si>
-    <t>MULTILAB</t>
-  </si>
-  <si>
-    <t>Sonda Portátil</t>
-  </si>
-  <si>
-    <t>Sonda Serie MultiLab</t>
-  </si>
-  <si>
-    <t>Hidrologia</t>
+    <t>Midas</t>
+  </si>
+  <si>
+    <t>Detector Fixo</t>
+  </si>
+  <si>
+    <t>SSO</t>
   </si>
 </sst>
 </file>
@@ -516,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
@@ -589,61 +601,64 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G2" s="2">
-        <v>45880</v>
+        <v>45904</v>
       </c>
       <c r="H2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K2" t="s">
-        <v>33</v>
+        <v>38</v>
+      </c>
+      <c r="L2" t="s">
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="N2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="O2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="P2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="R2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="S2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="T2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -651,61 +666,64 @@
         <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G3" s="2">
-        <v>45880</v>
+        <v>45904</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>38</v>
+      </c>
+      <c r="L3" t="s">
+        <v>38</v>
       </c>
       <c r="M3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="N3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="O3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="P3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="R3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="S3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="T3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="U3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -713,61 +731,194 @@
         <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="2">
+        <v>45904</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4" t="s">
+        <v>40</v>
+      </c>
+      <c r="O4" t="s">
+        <v>41</v>
+      </c>
+      <c r="P4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>43</v>
+      </c>
+      <c r="R4" t="s">
+        <v>44</v>
+      </c>
+      <c r="S4" t="s">
+        <v>46</v>
+      </c>
+      <c r="T4" t="s">
+        <v>49</v>
+      </c>
+      <c r="U4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
         <v>29</v>
       </c>
-      <c r="F4" t="s">
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="2">
+        <v>45904</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" t="s">
+        <v>40</v>
+      </c>
+      <c r="O5" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>43</v>
+      </c>
+      <c r="R5" t="s">
+        <v>45</v>
+      </c>
+      <c r="S5" t="s">
+        <v>47</v>
+      </c>
+      <c r="T5" t="s">
+        <v>49</v>
+      </c>
+      <c r="U5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="2">
-        <v>45880</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="C6" t="s">
         <v>31</v>
       </c>
-      <c r="I4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="D6" t="s">
         <v>33</v>
       </c>
-      <c r="M4" t="s">
+      <c r="E6" t="s">
         <v>34</v>
       </c>
-      <c r="N4" t="s">
+      <c r="F6" t="s">
         <v>35</v>
       </c>
-      <c r="O4" t="s">
+      <c r="G6" s="2">
+        <v>45904</v>
+      </c>
+      <c r="H6" t="s">
         <v>36</v>
       </c>
-      <c r="P4" t="s">
+      <c r="I6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" t="s">
         <v>37</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="K6" t="s">
         <v>38</v>
       </c>
-      <c r="R4" t="s">
+      <c r="L6" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" t="s">
         <v>40</v>
       </c>
-      <c r="S4" t="s">
+      <c r="O6" t="s">
+        <v>41</v>
+      </c>
+      <c r="P6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q6" t="s">
         <v>43</v>
       </c>
-      <c r="T4" t="s">
+      <c r="R6" t="s">
         <v>45</v>
       </c>
-      <c r="U4" t="s">
-        <v>46</v>
+      <c r="S6" t="s">
+        <v>48</v>
+      </c>
+      <c r="T6" t="s">
+        <v>49</v>
+      </c>
+      <c r="U6" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Conversões.xlsx
+++ b/Conversões.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="31">
   <si>
     <t>Código Produto</t>
   </si>
@@ -22,9 +22,6 @@
     <t>Descrição Produto</t>
   </si>
   <si>
-    <t>Qtde Atendida</t>
-  </si>
-  <si>
     <t>Operação</t>
   </si>
   <si>
@@ -52,21 +49,9 @@
     <t>Gerente Comercial-Pedido</t>
   </si>
   <si>
-    <t>Aplicação Mat./Serv.</t>
-  </si>
-  <si>
     <t>Cliente</t>
   </si>
   <si>
-    <t>Nome Cliente</t>
-  </si>
-  <si>
-    <t>Cidade</t>
-  </si>
-  <si>
-    <t>UF</t>
-  </si>
-  <si>
     <t>Tipo de Mercadoria</t>
   </si>
   <si>
@@ -79,46 +64,19 @@
     <t>Negócio</t>
   </si>
   <si>
-    <t>HONMMS-G2</t>
-  </si>
-  <si>
-    <t>HONMMS-TR</t>
-  </si>
-  <si>
-    <t>HONMMS-D2</t>
-  </si>
-  <si>
-    <t>ANGLTA2051WJ24V-IND</t>
-  </si>
-  <si>
-    <t>HONMMT-01</t>
-  </si>
-  <si>
-    <t>SENSOR ELETROQUIMICO DE H2 PARA ANALISADOR DE GÁS MODELO MIDAS M</t>
-  </si>
-  <si>
-    <t>SENSOR IR DE CO2 PARA ANALISADOR DE GÁS MODELO MIDAS M</t>
-  </si>
-  <si>
-    <t>SENSOR DE OXIGÊNIO PARA USO NO ANALISADOR DE GASES MODELO MIDAS M</t>
-  </si>
-  <si>
-    <t>SIRENE P/ SISTEMA DE DETECÇÃO FIXA SAV-C 24V</t>
-  </si>
-  <si>
-    <t>ANALISADOR FIXO PARA 4 GASES - MODELO MIDAS M</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PVEN - PEDIDO DE VENDA</t>
-  </si>
-  <si>
-    <t>133701</t>
+    <t>QED-AP4-RET</t>
+  </si>
+  <si>
+    <t>Teste Retenção (Neimar)</t>
+  </si>
+  <si>
+    <t>PVEN</t>
+  </si>
+  <si>
+    <t>RET-Test</t>
+  </si>
+  <si>
+    <t>999999</t>
   </si>
   <si>
     <t>FATURADO</t>
@@ -127,46 +85,28 @@
     <t>100</t>
   </si>
   <si>
-    <t>ANDREY.ANDRADE</t>
-  </si>
-  <si>
-    <t>LEONARDO DO CARMO</t>
-  </si>
-  <si>
-    <t>DEPART. DETECÇÃO FIXA GASES</t>
-  </si>
-  <si>
-    <t>22853</t>
-  </si>
-  <si>
-    <t>AMYRIS FERMENTACAO DE PERFORMANCE LTDA</t>
-  </si>
-  <si>
-    <t>BARRA BONITA</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>Reposição</t>
+    <t>DENER.MARTINS</t>
+  </si>
+  <si>
+    <t>Cliente Teste1</t>
+  </si>
+  <si>
+    <t>Cliente Teste2</t>
+  </si>
+  <si>
+    <t>Cliente Teste3</t>
   </si>
   <si>
     <t>Produto</t>
   </si>
   <si>
-    <t>Sensor</t>
-  </si>
-  <si>
-    <t>Acessório</t>
-  </si>
-  <si>
-    <t>Midas</t>
-  </si>
-  <si>
-    <t>Detector Fixo</t>
-  </si>
-  <si>
-    <t>SSO</t>
+    <t>Auto Pump</t>
+  </si>
+  <si>
+    <t>Elevador de Liquidos Fixo</t>
+  </si>
+  <si>
+    <t>Remediação</t>
   </si>
 </sst>
 </file>
@@ -528,10 +468,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -580,345 +520,313 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="C2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="2">
+        <v>45918</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="2">
+        <v>45918</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="2">
+        <v>45918</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="2">
+        <v>45918</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="2">
+        <v>45918</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O6" t="s">
+        <v>29</v>
+      </c>
+      <c r="P6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
         <v>20</v>
       </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45918</v>
+      </c>
+      <c r="G7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" t="s">
+        <v>28</v>
+      </c>
+      <c r="O7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P7" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:21">
-      <c r="A2" t="s">
+    <row r="8" spans="1:16">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="2">
-        <v>45904</v>
-      </c>
-      <c r="H2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N2" t="s">
-        <v>40</v>
-      </c>
-      <c r="O2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R2" t="s">
-        <v>44</v>
-      </c>
-      <c r="S2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T2" t="s">
-        <v>49</v>
-      </c>
-      <c r="U2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="F8" s="2">
+        <v>45918</v>
+      </c>
+      <c r="G8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" t="s">
         <v>27</v>
       </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="2">
-        <v>45904</v>
-      </c>
-      <c r="H3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P3" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>43</v>
-      </c>
-      <c r="R3" t="s">
-        <v>44</v>
-      </c>
-      <c r="S3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T3" t="s">
-        <v>49</v>
-      </c>
-      <c r="U3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="N8" t="s">
         <v>28</v>
       </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="2">
-        <v>45904</v>
-      </c>
-      <c r="H4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" t="s">
-        <v>37</v>
-      </c>
-      <c r="K4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L4" t="s">
-        <v>38</v>
-      </c>
-      <c r="M4" t="s">
-        <v>39</v>
-      </c>
-      <c r="N4" t="s">
-        <v>40</v>
-      </c>
-      <c r="O4" t="s">
-        <v>41</v>
-      </c>
-      <c r="P4" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>43</v>
-      </c>
-      <c r="R4" t="s">
-        <v>44</v>
-      </c>
-      <c r="S4" t="s">
-        <v>46</v>
-      </c>
-      <c r="T4" t="s">
-        <v>49</v>
-      </c>
-      <c r="U4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="O8" t="s">
         <v>29</v>
       </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="2">
-        <v>45904</v>
-      </c>
-      <c r="H5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" t="s">
-        <v>37</v>
-      </c>
-      <c r="K5" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" t="s">
-        <v>38</v>
-      </c>
-      <c r="M5" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" t="s">
-        <v>40</v>
-      </c>
-      <c r="O5" t="s">
-        <v>41</v>
-      </c>
-      <c r="P5" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>43</v>
-      </c>
-      <c r="R5" t="s">
-        <v>45</v>
-      </c>
-      <c r="S5" t="s">
-        <v>47</v>
-      </c>
-      <c r="T5" t="s">
-        <v>49</v>
-      </c>
-      <c r="U5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="P8" t="s">
         <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="2">
-        <v>45904</v>
-      </c>
-      <c r="H6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K6" t="s">
-        <v>38</v>
-      </c>
-      <c r="L6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M6" t="s">
-        <v>39</v>
-      </c>
-      <c r="N6" t="s">
-        <v>40</v>
-      </c>
-      <c r="O6" t="s">
-        <v>41</v>
-      </c>
-      <c r="P6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>43</v>
-      </c>
-      <c r="R6" t="s">
-        <v>45</v>
-      </c>
-      <c r="S6" t="s">
-        <v>48</v>
-      </c>
-      <c r="T6" t="s">
-        <v>49</v>
-      </c>
-      <c r="U6" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Conversões.xlsx
+++ b/Conversões.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
   <si>
     <t>Código Produto</t>
   </si>
@@ -73,7 +73,10 @@
     <t>PVEN</t>
   </si>
   <si>
-    <t>FC-Base3</t>
+    <t>999999</t>
+  </si>
+  <si>
+    <t>999998</t>
   </si>
   <si>
     <t>FATURADO</t>
@@ -91,7 +94,7 @@
     <t>André Camargo</t>
   </si>
   <si>
-    <t>Cliente Teste</t>
+    <t>005309</t>
   </si>
   <si>
     <t>Produto</t>
@@ -465,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -532,37 +535,84 @@
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" s="2">
         <v>45915</v>
       </c>
       <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
         <v>21</v>
       </c>
-      <c r="H2" t="s">
+      <c r="F3" s="2">
+        <v>45915</v>
+      </c>
+      <c r="G3" t="s">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="H3" t="s">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="I3" t="s">
         <v>24</v>
       </c>
-      <c r="L2" t="s">
+      <c r="J3" t="s">
         <v>25</v>
       </c>
-      <c r="M2" t="s">
+      <c r="L3" t="s">
         <v>26</v>
       </c>
-      <c r="N2" t="s">
+      <c r="M3" t="s">
         <v>27</v>
       </c>
-      <c r="O2" t="s">
+      <c r="N3" t="s">
         <v>28</v>
       </c>
-      <c r="P2" t="s">
+      <c r="O3" t="s">
         <v>29</v>
+      </c>
+      <c r="P3" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Conversões.xlsx
+++ b/Conversões.xlsx
@@ -1,141 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
-  <si>
-    <t>Código Produto</t>
-  </si>
-  <si>
-    <t>Descrição Produto</t>
-  </si>
-  <si>
-    <t>Operação</t>
-  </si>
-  <si>
-    <t>Processo</t>
-  </si>
-  <si>
-    <t>Status Processo</t>
-  </si>
-  <si>
-    <t>Data Aceite</t>
-  </si>
-  <si>
-    <t>Valor Orçado</t>
-  </si>
-  <si>
-    <t>Valor Realizado</t>
-  </si>
-  <si>
-    <t>Consultor Interno</t>
-  </si>
-  <si>
-    <t>Representante-pedido</t>
-  </si>
-  <si>
-    <t>Gerente Comercial-Pedido</t>
-  </si>
-  <si>
-    <t>Cliente</t>
-  </si>
-  <si>
-    <t>Tipo de Mercadoria</t>
-  </si>
-  <si>
-    <t>Subgrupo</t>
-  </si>
-  <si>
-    <t>Grupo</t>
-  </si>
-  <si>
-    <t>Negócio</t>
-  </si>
-  <si>
-    <t>HON-MCXL-BASE</t>
-  </si>
-  <si>
-    <t>Base Teste FC</t>
-  </si>
-  <si>
-    <t>PVEN</t>
-  </si>
-  <si>
-    <t>999999</t>
-  </si>
-  <si>
-    <t>999998</t>
-  </si>
-  <si>
-    <t>FATURADO</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>Andrey Andrade</t>
-  </si>
-  <si>
-    <t>André Camargo</t>
-  </si>
-  <si>
-    <t>005309</t>
-  </si>
-  <si>
-    <t>Produto</t>
-  </si>
-  <si>
-    <t>MicroClip</t>
-  </si>
-  <si>
-    <t>Detector Portátil</t>
-  </si>
-  <si>
-    <t>SSO</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -150,36 +49,94 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -467,155 +424,249 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Código Produto</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Descrição Produto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Operação</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Processo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status Processo</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Data Aceite</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Valor Orçado</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Valor Realizado</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Consultor Interno</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Representante-pedido</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Gerente Comercial-Pedido</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo de Mercadoria</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Subgrupo</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Negócio</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:16">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="2">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HON-MCXL-BASE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Base Teste FC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PVEN</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>999999</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>FATURADO</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>45915</v>
       </c>
-      <c r="G2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" t="s">
-        <v>29</v>
-      </c>
-      <c r="P2" t="s">
-        <v>30</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Andrey Andrade</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>André Camargo</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>005309</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>MicroClip</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Detector Portátil</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SSO</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:16">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="2">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HON-MCXL-BASE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Base Teste FC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PVEN</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>999998</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FATURADO</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
         <v>45915</v>
       </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" t="s">
-        <v>30</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Andrey Andrade</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>André Camargo</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>005309</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>MicroClip</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Detector Portátil</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SSO</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Conversões.xlsx
+++ b/Conversões.xlsx
@@ -1,40 +1,141 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
+  <si>
+    <t>Código Produto</t>
+  </si>
+  <si>
+    <t>Descrição Produto</t>
+  </si>
+  <si>
+    <t>Operação</t>
+  </si>
+  <si>
+    <t>Processo</t>
+  </si>
+  <si>
+    <t>Status Processo</t>
+  </si>
+  <si>
+    <t>Data Aceite</t>
+  </si>
+  <si>
+    <t>Valor Orçado</t>
+  </si>
+  <si>
+    <t>Valor Realizado</t>
+  </si>
+  <si>
+    <t>Consultor Interno</t>
+  </si>
+  <si>
+    <t>Representante-pedido</t>
+  </si>
+  <si>
+    <t>Gerente Comercial-Pedido</t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>Tipo de Mercadoria</t>
+  </si>
+  <si>
+    <t>Subgrupo</t>
+  </si>
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>Negócio</t>
+  </si>
+  <si>
+    <t>HON-MCXL-BASE</t>
+  </si>
+  <si>
+    <t>Base Teste FC</t>
+  </si>
+  <si>
+    <t>PVEN</t>
+  </si>
+  <si>
+    <t>999999</t>
+  </si>
+  <si>
+    <t>999998</t>
+  </si>
+  <si>
+    <t>FATURADO</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>Andrey Andrade</t>
+  </si>
+  <si>
+    <t>André Camargo</t>
+  </si>
+  <si>
+    <t>005309</t>
+  </si>
+  <si>
+    <t>Produto</t>
+  </si>
+  <si>
+    <t>MicroClip</t>
+  </si>
+  <si>
+    <t>Detector Portátil</t>
+  </si>
+  <si>
+    <t>SSO</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,94 +150,36 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -424,249 +467,155 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Código Produto</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Descrição Produto</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Operação</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Processo</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Status Processo</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Data Aceite</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Valor Orçado</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Valor Realizado</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Consultor Interno</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Representante-pedido</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Gerente Comercial-Pedido</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo de Mercadoria</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Subgrupo</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Grupo</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Negócio</t>
-        </is>
+    <row r="1" spans="1:16">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HON-MCXL-BASE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Base Teste FC</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>PVEN</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>999999</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>FATURADO</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="2">
         <v>45915</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Andrey Andrade</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>André Camargo</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>005309</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>MicroClip</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Detector Portátil</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>SSO</t>
-        </is>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>HON-MCXL-BASE</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Base Teste FC</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>PVEN</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>999998</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FATURADO</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n">
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="2">
         <v>45915</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Andrey Andrade</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>André Camargo</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>005309</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>MicroClip</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Detector Portátil</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>SSO</t>
-        </is>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Conversões.xlsx
+++ b/Conversões.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="39">
   <si>
     <t>Código Produto</t>
   </si>
@@ -67,9 +67,15 @@
     <t>HON-MCXL-BASE</t>
   </si>
   <si>
+    <t>HON-SENS-CS</t>
+  </si>
+  <si>
     <t>Base Teste FC</t>
   </si>
   <si>
+    <t>Teste Cross Selling</t>
+  </si>
+  <si>
     <t>PVEN</t>
   </si>
   <si>
@@ -79,6 +85,9 @@
     <t>999998</t>
   </si>
   <si>
+    <t>CS-Test</t>
+  </si>
+  <si>
     <t>FATURADO</t>
   </si>
   <si>
@@ -91,16 +100,31 @@
     <t>Andrey Andrade</t>
   </si>
   <si>
+    <t>Rosilene</t>
+  </si>
+  <si>
     <t>André Camargo</t>
   </si>
   <si>
+    <t>MATEUS BORRO MACHADO</t>
+  </si>
+  <si>
     <t>005309</t>
   </si>
   <si>
+    <t>Cliente CS</t>
+  </si>
+  <si>
     <t>Produto</t>
   </si>
   <si>
+    <t>Reposição</t>
+  </si>
+  <si>
     <t>MicroClip</t>
+  </si>
+  <si>
+    <t>Sensor</t>
   </si>
   <si>
     <t>Detector Portátil</t>
@@ -468,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -526,46 +550,46 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F2" s="2">
         <v>45915</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="M2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="N2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="P2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -573,46 +597,96 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F3" s="2">
         <v>45915</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
         <v>23</v>
       </c>
-      <c r="I3" t="s">
+      <c r="E4" t="s">
         <v>24</v>
       </c>
-      <c r="J3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="F4" s="2">
+        <v>45920</v>
+      </c>
+      <c r="G4" t="s">
         <v>26</v>
       </c>
-      <c r="M3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
         <v>28</v>
       </c>
-      <c r="O3" t="s">
+      <c r="J4" t="s">
         <v>29</v>
       </c>
-      <c r="P3" t="s">
+      <c r="K4" t="s">
         <v>30</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" t="s">
+        <v>37</v>
+      </c>
+      <c r="P4" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
